--- a/AAII_Financials/Yearly/DOCU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOCU_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/DOCU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOCU_YR_FIN.xlsx
@@ -656,59 +656,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
         <v>44957</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44592</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44227</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43861</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43496</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43131</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42766</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42400</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -718,39 +718,42 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2761900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2515900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2107200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1453000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>974000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>701000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>518500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>381500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>250500</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -760,39 +763,42 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>571900</v>
+      </c>
+      <c r="E9" s="3">
         <v>535000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>466500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>364100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>243200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>192400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>118300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>102500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>73900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -802,39 +808,42 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2190000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1980900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1640800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1089000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>730700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>508500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>400200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>279000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>176600</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,9 +853,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,38 +875,39 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>539500</v>
+      </c>
+      <c r="E12" s="3">
         <v>480600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>393400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>271500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>185600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>186000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>92400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>89700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>62300</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,24 +962,27 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E14" s="3">
         <v>29400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>33800</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -979,8 +998,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -988,39 +1007,42 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E15" s="3">
         <v>11100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2000</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1030,9 +1052,12 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,38 +1071,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2730200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2603900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2169100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1660700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1167500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1127300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>570200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>497300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>369800</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,39 +1113,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-88000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-61900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-207600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-193500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-426300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-51700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-115800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-119300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1129,9 +1158,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,38 +1180,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E20" s="3">
         <v>4500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>19200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3500</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,36 +1222,39 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>195600</v>
+      </c>
+      <c r="E21" s="3">
         <v>2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>21400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-127600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-124100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-379300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-86000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1231,39 +1267,42 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>6400</v>
+        <v>6800</v>
       </c>
       <c r="E22" s="3">
         <v>6400</v>
       </c>
       <c r="F22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="G22" s="3">
         <v>30800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>29300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>600</v>
       </c>
       <c r="J22" s="3">
         <v>600</v>
       </c>
       <c r="K22" s="3">
+        <v>600</v>
+      </c>
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1273,39 +1312,42 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>93700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-89900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-66900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-229500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-203600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-428200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-49100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-115100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-123600</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1315,39 +1357,42 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E24" s="3">
         <v>7600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1357,9 +1402,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,39 +1447,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-97500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-70000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-243300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-208400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-426500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-52300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-115400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-122600</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1441,39 +1492,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-97500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-70000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-243300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-208400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-426800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-53700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-116900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-124000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1483,9 +1537,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1567,9 +1627,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,39 +1717,42 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-19200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3500</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1693,39 +1762,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-97500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-70000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-243300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-208400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-426800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-53700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-116900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-124000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,9 +1807,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,39 +1852,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-97500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-70000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-243300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-208400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-426800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-53700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-116900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-124000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1819,44 +1897,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
         <v>44957</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44592</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44227</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43861</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43496</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43131</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42766</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42400</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1866,9 +1947,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,40 +1988,41 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>797100</v>
+      </c>
+      <c r="E41" s="3">
         <v>721900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>509100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>566100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>241200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>517800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>256900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>190600</v>
-      </c>
-      <c r="K41" s="3">
-        <v>228500</v>
       </c>
       <c r="L41" s="3">
         <v>228500</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
+      <c r="M41" s="3">
+        <v>228500</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
@@ -1944,30 +2030,33 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>248400</v>
+      </c>
+      <c r="E42" s="3">
         <v>309800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>293800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>207400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>414900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>251200</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1983,44 +2072,47 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>455200</v>
+      </c>
+      <c r="E43" s="3">
         <v>529400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>453500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>340500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>250300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>185200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>138000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>103100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>80400</v>
       </c>
       <c r="L43" s="3">
         <v>80400</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
+      <c r="M43" s="3">
+        <v>80400</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
@@ -2028,9 +2120,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2070,41 +2165,44 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E45" s="3">
         <v>70000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>63200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>48400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>30300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>20500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>24500</v>
       </c>
       <c r="L45" s="3">
         <v>24500</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>24500</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
@@ -2112,41 +2210,44 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1567700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1631000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1319600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1162300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>943900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>984500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>418800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>314100</v>
-      </c>
-      <c r="K46" s="3">
-        <v>333300</v>
       </c>
       <c r="L46" s="3">
         <v>333300</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
+      <c r="M46" s="3">
+        <v>333300</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
@@ -2154,30 +2255,33 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>135200</v>
+      </c>
+      <c r="E47" s="3">
         <v>198500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>107300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>99300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>240600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>164200</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2193,44 +2297,47 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>368400</v>
+      </c>
+      <c r="E48" s="3">
         <v>341400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>310700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>324400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>278100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>75800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>63000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>63700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>36800</v>
       </c>
       <c r="L48" s="3">
         <v>36800</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
+      <c r="M48" s="3">
+        <v>36800</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
@@ -2238,41 +2345,44 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>404000</v>
+      </c>
+      <c r="E49" s="3">
         <v>423900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>453900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>472000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>251400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>269400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>51500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>58800</v>
-      </c>
-      <c r="K49" s="3">
-        <v>66900</v>
       </c>
       <c r="L49" s="3">
         <v>66900</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>66900</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2280,9 +2390,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,41 +2480,44 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>496000</v>
+      </c>
+      <c r="E52" s="3">
         <v>417900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>349800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>278500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>177100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>121400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>86700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>63100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>49400</v>
       </c>
       <c r="L52" s="3">
         <v>49400</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>49400</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2406,9 +2525,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,41 +2570,44 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2971300</v>
+      </c>
+      <c r="E54" s="3">
         <v>3012700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2541300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2336500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1891100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1615400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>620000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>499600</v>
-      </c>
-      <c r="K54" s="3">
-        <v>486500</v>
       </c>
       <c r="L54" s="3">
         <v>486500</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
+      <c r="M54" s="3">
+        <v>486500</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
@@ -2490,9 +2615,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,40 +2656,41 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E57" s="3">
         <v>24400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>52800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>37400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>13400</v>
       </c>
       <c r="L57" s="3">
         <v>13400</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>13400</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -2568,29 +2698,32 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>722900</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>20500</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2601,8 +2734,8 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2610,41 +2743,44 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1641600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1461000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1318800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1035300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>665800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>496700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>350100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>250800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>187400</v>
       </c>
       <c r="L59" s="3">
         <v>187400</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
+      <c r="M59" s="3">
+        <v>187400</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
@@ -2652,41 +2788,44 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1660600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2208300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1371600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1093200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>694000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>516300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>373800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>269900</v>
-      </c>
-      <c r="K60" s="3">
-        <v>200900</v>
       </c>
       <c r="L60" s="3">
         <v>200900</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
+      <c r="M60" s="3">
+        <v>200900</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
@@ -2694,9 +2833,12 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2704,20 +2846,20 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>718500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>696600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>465300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>438900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2736,41 +2878,44 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>180900</v>
+      </c>
+      <c r="E62" s="3">
         <v>187100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>175600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>221000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>185500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>45800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>37300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>31100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>17200</v>
       </c>
       <c r="L62" s="3">
         <v>17200</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>17200</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -2778,9 +2923,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,41 +3058,44 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1841600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2395400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2265800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2010800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1344800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1001100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>411100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>301000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>218000</v>
       </c>
       <c r="L66" s="3">
         <v>218000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
+      <c r="M66" s="3">
+        <v>218000</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
@@ -2946,9 +3103,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3070,19 +3237,19 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>547500</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>546000</v>
-      </c>
-      <c r="K70" s="3">
-        <v>544600</v>
       </c>
       <c r="L70" s="3">
         <v>544600</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>544600</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,41 +3302,44 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1670200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1598700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1438200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1380500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1137200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-928800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-502300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-450000</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-334600</v>
       </c>
       <c r="L72" s="3">
         <v>-334600</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
+      <c r="M72" s="3">
+        <v>-334600</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
@@ -3174,9 +3347,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,41 +3482,44 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1129700</v>
+      </c>
+      <c r="E76" s="3">
         <v>617300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>275500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>325700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>546300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>614400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-338600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-347300</v>
-      </c>
-      <c r="K76" s="3">
-        <v>-276200</v>
       </c>
       <c r="L76" s="3">
         <v>-276200</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
+      <c r="M76" s="3">
+        <v>-276200</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
@@ -3342,9 +3527,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,44 +3572,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
         <v>44957</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44592</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44227</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43861</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43496</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43131</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42766</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42400</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3431,39 +3622,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-97500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-70000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-243300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-208400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-426800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-53700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-116900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-124000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,9 +3667,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,35 +3689,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E83" s="3">
         <v>86300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>81900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>71100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>50200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>38000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>31700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>28500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,9 +3731,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,36 +3956,39 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>979500</v>
+      </c>
+      <c r="E89" s="3">
         <v>506800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>506500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>297000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>115700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>76100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>55000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3785,9 +4001,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,35 +4023,36 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-92400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-77700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-61400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-82400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-72000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-30400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-43300</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3845,9 +4065,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,36 +4155,39 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-191200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-162900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>81200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-321500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-664300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-40900</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3971,9 +4200,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4031,9 +4264,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,36 +4399,39 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-946000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-98300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-394600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-59000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-70500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>853100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>25700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4199,36 +4444,39 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4241,36 +4489,39 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E102" s="3">
         <v>213500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-56700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>324900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-276700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>260700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>66200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-38000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,7 +4534,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/DOCU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOCU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>DOCU</t>
   </si>
@@ -773,22 +773,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>571900</v>
+        <v>541300</v>
       </c>
       <c r="E9" s="3">
-        <v>535000</v>
+        <v>507100</v>
       </c>
       <c r="F9" s="3">
-        <v>466500</v>
+        <v>431600</v>
       </c>
       <c r="G9" s="3">
-        <v>364100</v>
+        <v>358200</v>
       </c>
       <c r="H9" s="3">
-        <v>243200</v>
+        <v>240700</v>
       </c>
       <c r="I9" s="3">
-        <v>192400</v>
+        <v>190400</v>
       </c>
       <c r="J9" s="3">
         <v>118300</v>
@@ -818,22 +818,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2190000</v>
+        <v>2220600</v>
       </c>
       <c r="E10" s="3">
-        <v>1980900</v>
+        <v>2008900</v>
       </c>
       <c r="F10" s="3">
-        <v>1640800</v>
+        <v>1675600</v>
       </c>
       <c r="G10" s="3">
-        <v>1089000</v>
+        <v>1094900</v>
       </c>
       <c r="H10" s="3">
-        <v>730700</v>
+        <v>733300</v>
       </c>
       <c r="I10" s="3">
-        <v>508500</v>
+        <v>510600</v>
       </c>
       <c r="J10" s="3">
         <v>400200</v>
@@ -975,10 +975,10 @@
         <v>31100</v>
       </c>
       <c r="E14" s="3">
-        <v>29400</v>
+        <v>33100</v>
       </c>
       <c r="F14" s="3">
-        <v>5100</v>
+        <v>-200</v>
       </c>
       <c r="G14" s="3">
         <v>33800</v>
@@ -986,8 +986,8 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>100</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10500</v>
+        <v>60000</v>
       </c>
       <c r="E15" s="3">
-        <v>11100</v>
+        <v>66600</v>
       </c>
       <c r="F15" s="3">
-        <v>13100</v>
+        <v>71600</v>
       </c>
       <c r="G15" s="3">
-        <v>14600</v>
+        <v>64900</v>
       </c>
       <c r="H15" s="3">
-        <v>12000</v>
+        <v>46100</v>
       </c>
       <c r="I15" s="3">
-        <v>7000</v>
+        <v>35200</v>
       </c>
       <c r="J15" s="3">
-        <v>3300</v>
+        <v>28200</v>
       </c>
       <c r="K15" s="3">
         <v>3400</v>
@@ -1078,22 +1078,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2730200</v>
+        <v>2699100</v>
       </c>
       <c r="E17" s="3">
-        <v>2603900</v>
+        <v>2574500</v>
       </c>
       <c r="F17" s="3">
-        <v>2169100</v>
+        <v>2164000</v>
       </c>
       <c r="G17" s="3">
-        <v>1660700</v>
+        <v>1626900</v>
       </c>
       <c r="H17" s="3">
         <v>1167500</v>
       </c>
       <c r="I17" s="3">
-        <v>1127300</v>
+        <v>1127200</v>
       </c>
       <c r="J17" s="3">
         <v>570200</v>
@@ -1123,22 +1123,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>31600</v>
+        <v>62700</v>
       </c>
       <c r="E18" s="3">
-        <v>-88000</v>
+        <v>-58600</v>
       </c>
       <c r="F18" s="3">
-        <v>-61900</v>
+        <v>-56800</v>
       </c>
       <c r="G18" s="3">
-        <v>-207600</v>
+        <v>-173900</v>
       </c>
       <c r="H18" s="3">
         <v>-193500</v>
       </c>
       <c r="I18" s="3">
-        <v>-426300</v>
+        <v>-426200</v>
       </c>
       <c r="J18" s="3">
         <v>-51700</v>
@@ -1186,26 +1186,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>68900</v>
-      </c>
-      <c r="E20" s="3">
-        <v>4500</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>8900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>19200</v>
+        <v>3900</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
-        <v>9000</v>
+        <v>-9000</v>
       </c>
       <c r="J20" s="3">
-        <v>3100</v>
+        <v>-2000</v>
       </c>
       <c r="K20" s="3">
         <v>1400</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>195600</v>
+        <v>122700</v>
       </c>
       <c r="E21" s="3">
-        <v>2800</v>
+        <v>7900</v>
       </c>
       <c r="F21" s="3">
-        <v>21400</v>
+        <v>11000</v>
       </c>
       <c r="G21" s="3">
-        <v>-127600</v>
+        <v>-109000</v>
       </c>
       <c r="H21" s="3">
-        <v>-124100</v>
+        <v>-147400</v>
       </c>
       <c r="I21" s="3">
-        <v>-379300</v>
+        <v>-382000</v>
       </c>
       <c r="J21" s="3">
-        <v>-16800</v>
+        <v>-21500</v>
       </c>
       <c r="K21" s="3">
         <v>-86000</v>
@@ -1726,26 +1726,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-68900</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-4500</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-19200</v>
+        <v>-3900</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
-        <v>-9000</v>
+        <v>9000</v>
       </c>
       <c r="J32" s="3">
-        <v>-3100</v>
+        <v>2000</v>
       </c>
       <c r="K32" s="3">
         <v>-1400</v>
@@ -1787,10 +1787,10 @@
         <v>-208400</v>
       </c>
       <c r="I33" s="3">
-        <v>-426800</v>
+        <v>-426500</v>
       </c>
       <c r="J33" s="3">
-        <v>-53700</v>
+        <v>-52300</v>
       </c>
       <c r="K33" s="3">
         <v>-116900</v>
@@ -1877,10 +1877,10 @@
         <v>-208400</v>
       </c>
       <c r="I35" s="3">
-        <v>-426800</v>
+        <v>-426500</v>
       </c>
       <c r="J35" s="3">
-        <v>-53700</v>
+        <v>-52300</v>
       </c>
       <c r="K35" s="3">
         <v>-116900</v>
@@ -2049,7 +2049,7 @@
         <v>293800</v>
       </c>
       <c r="G42" s="3">
-        <v>207400</v>
+        <v>207500</v>
       </c>
       <c r="H42" s="3">
         <v>414900</v>
@@ -2057,8 +2057,8 @@
       <c r="I42" s="3">
         <v>251200</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -2129,26 +2129,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>67000</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>70000</v>
+        <v>4500</v>
       </c>
       <c r="F45" s="3">
-        <v>63200</v>
+        <v>3300</v>
       </c>
       <c r="G45" s="3">
-        <v>48400</v>
+        <v>2400</v>
       </c>
       <c r="H45" s="3">
-        <v>37400</v>
+        <v>2400</v>
       </c>
       <c r="I45" s="3">
-        <v>30300</v>
+        <v>11600</v>
       </c>
       <c r="J45" s="3">
-        <v>23900</v>
+        <v>7300</v>
       </c>
       <c r="K45" s="3">
         <v>20500</v>
@@ -2274,10 +2274,10 @@
         <v>107300</v>
       </c>
       <c r="G47" s="3">
-        <v>99300</v>
+        <v>98700</v>
       </c>
       <c r="H47" s="3">
-        <v>240600</v>
+        <v>255200</v>
       </c>
       <c r="I47" s="3">
         <v>164200</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>496000</v>
+        <v>21600</v>
       </c>
       <c r="E52" s="3">
-        <v>417900</v>
+        <v>17500</v>
       </c>
       <c r="F52" s="3">
-        <v>349800</v>
+        <v>15300</v>
       </c>
       <c r="G52" s="3">
-        <v>278500</v>
+        <v>14600</v>
       </c>
       <c r="H52" s="3">
-        <v>177100</v>
+        <v>8300</v>
       </c>
       <c r="I52" s="3">
-        <v>121400</v>
+        <v>7500</v>
       </c>
       <c r="J52" s="3">
-        <v>86700</v>
+        <v>7500</v>
       </c>
       <c r="K52" s="3">
         <v>63100</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>22200</v>
       </c>
       <c r="E58" s="3">
-        <v>722900</v>
+        <v>746900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>37400</v>
       </c>
       <c r="G58" s="3">
-        <v>20500</v>
+        <v>53400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1641600</v>
+        <v>1320100</v>
       </c>
       <c r="E59" s="3">
-        <v>1461000</v>
+        <v>1172900</v>
       </c>
       <c r="F59" s="3">
-        <v>1318800</v>
+        <v>1029900</v>
       </c>
       <c r="G59" s="3">
-        <v>1035300</v>
+        <v>779600</v>
       </c>
       <c r="H59" s="3">
-        <v>665800</v>
+        <v>507600</v>
       </c>
       <c r="I59" s="3">
-        <v>496700</v>
+        <v>397400</v>
       </c>
       <c r="J59" s="3">
-        <v>350100</v>
+        <v>283500</v>
       </c>
       <c r="K59" s="3">
         <v>250800</v>
@@ -2843,19 +2843,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>120800</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>141300</v>
       </c>
       <c r="F61" s="3">
-        <v>718500</v>
+        <v>844800</v>
       </c>
       <c r="G61" s="3">
-        <v>696600</v>
+        <v>862300</v>
       </c>
       <c r="H61" s="3">
-        <v>465300</v>
+        <v>627800</v>
       </c>
       <c r="I61" s="3">
         <v>438900</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>180900</v>
+        <v>21300</v>
       </c>
       <c r="E62" s="3">
-        <v>187100</v>
+        <v>18100</v>
       </c>
       <c r="F62" s="3">
-        <v>175600</v>
+        <v>23300</v>
       </c>
       <c r="G62" s="3">
-        <v>221000</v>
+        <v>32300</v>
       </c>
       <c r="H62" s="3">
-        <v>185500</v>
+        <v>6700</v>
       </c>
       <c r="I62" s="3">
-        <v>45800</v>
+        <v>33900</v>
       </c>
       <c r="J62" s="3">
-        <v>37300</v>
+        <v>27100</v>
       </c>
       <c r="K62" s="3">
         <v>31100</v>
@@ -3647,10 +3647,10 @@
         <v>-208400</v>
       </c>
       <c r="I81" s="3">
-        <v>-426800</v>
+        <v>-426500</v>
       </c>
       <c r="J81" s="3">
-        <v>-53700</v>
+        <v>-52300</v>
       </c>
       <c r="K81" s="3">
         <v>-116900</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>95100</v>
+        <v>40600</v>
       </c>
       <c r="E83" s="3">
-        <v>86300</v>
+        <v>45800</v>
       </c>
       <c r="F83" s="3">
-        <v>81900</v>
+        <v>46800</v>
       </c>
       <c r="G83" s="3">
-        <v>71100</v>
+        <v>39300</v>
       </c>
       <c r="H83" s="3">
-        <v>50200</v>
+        <v>28400</v>
       </c>
       <c r="I83" s="3">
-        <v>38000</v>
+        <v>22100</v>
       </c>
       <c r="J83" s="3">
-        <v>31700</v>
+        <v>18100</v>
       </c>
       <c r="K83" s="3">
         <v>28500</v>

--- a/AAII_Financials/Yearly/DOCU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOCU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>DOCU</t>
   </si>
@@ -656,62 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44957</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44592</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43861</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43496</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43131</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42766</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42400</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,42 +721,45 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2976700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2761900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2515900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2107200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1453000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>974000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>701000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>518500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>381500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>250500</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -766,42 +769,45 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>541300</v>
+        <v>617800</v>
       </c>
       <c r="E9" s="3">
-        <v>507100</v>
+        <v>569600</v>
       </c>
       <c r="F9" s="3">
+        <v>532800</v>
+      </c>
+      <c r="G9" s="3">
         <v>431600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>358200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>240700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>190400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>118300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>102500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>73900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,42 +817,45 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2220600</v>
+        <v>2359000</v>
       </c>
       <c r="E10" s="3">
-        <v>2008900</v>
+        <v>2192200</v>
       </c>
       <c r="F10" s="3">
+        <v>1983100</v>
+      </c>
+      <c r="G10" s="3">
         <v>1675600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1094900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>733300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>510600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>400200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>279000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>176600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,9 +865,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,41 +888,42 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>588500</v>
+      </c>
+      <c r="E12" s="3">
         <v>539500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>480600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>393400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>271500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>185600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>186000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>92400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>89700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>62300</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,33 +981,36 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E14" s="3">
         <v>31100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>33100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>33800</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1001,8 +1020,8 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1010,42 +1029,45 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E15" s="3">
         <v>60000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>66600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>71600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>64900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>46100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>35200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>28200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2000</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1055,9 +1077,12 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,41 +1097,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2742800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2699100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2574500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2164000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1626900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1167500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1127200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>570200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>497300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>369800</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1116,42 +1142,45 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>234000</v>
+      </c>
+      <c r="E18" s="3">
         <v>62700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-58600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-56800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-173900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-193500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-426200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-51700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-115800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-119300</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1161,9 +1190,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,8 +1213,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1192,30 +1225,30 @@
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>3900</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>-9000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3500</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,39 +1258,42 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>286600</v>
+      </c>
+      <c r="E21" s="3">
         <v>122700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-109000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-147400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-382000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-21500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-86000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,42 +1306,45 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="3">
         <v>6800</v>
-      </c>
-      <c r="E22" s="3">
-        <v>6400</v>
       </c>
       <c r="F22" s="3">
         <v>6400</v>
       </c>
       <c r="G22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="H22" s="3">
         <v>30800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>29300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10800</v>
-      </c>
-      <c r="J22" s="3">
-        <v>600</v>
       </c>
       <c r="K22" s="3">
         <v>600</v>
       </c>
       <c r="L22" s="3">
+        <v>600</v>
+      </c>
+      <c r="M22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1315,42 +1354,45 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>247900</v>
+      </c>
+      <c r="E23" s="3">
         <v>93700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-89900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-66900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-229500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-203600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-428200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-49100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-115100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-123600</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1360,42 +1402,45 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-819900</v>
+      </c>
+      <c r="E24" s="3">
         <v>19700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1000</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1405,9 +1450,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,42 +1498,45 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1067900</v>
+      </c>
+      <c r="E26" s="3">
         <v>74000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-97500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-70000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-243300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-208400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-426500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-52300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-115400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-122600</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1495,42 +1546,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1067900</v>
+      </c>
+      <c r="E27" s="3">
         <v>74000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-97500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-70000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-243300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-208400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-426800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-53700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-116900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-124000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,9 +1594,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,9 +1786,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1732,30 +1801,30 @@
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>-3900</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>9000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3500</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,42 +1834,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1067900</v>
+      </c>
+      <c r="E33" s="3">
         <v>74000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-97500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-70000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-243300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-208400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-426500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-52300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-116900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-124000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,9 +1882,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,42 +1930,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1067900</v>
+      </c>
+      <c r="E35" s="3">
         <v>74000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-97500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-70000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-243300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-208400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-426500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-52300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-116900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-124000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1900,47 +1978,50 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44957</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44592</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43861</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43496</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43131</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42766</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42400</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1950,9 +2031,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,43 +2074,44 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>648600</v>
+      </c>
+      <c r="E41" s="3">
         <v>797100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>721900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>509100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>566100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>241200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>517800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>256900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>190600</v>
-      </c>
-      <c r="L41" s="3">
-        <v>228500</v>
       </c>
       <c r="M41" s="3">
         <v>228500</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
+      <c r="N41" s="3">
+        <v>228500</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
@@ -2033,35 +2119,38 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>314900</v>
+      </c>
+      <c r="E42" s="3">
         <v>248400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>309800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>293800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>207500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>414900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>251200</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -2075,47 +2164,50 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>443300</v>
+      </c>
+      <c r="E43" s="3">
         <v>455200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>529400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>453500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>340500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>250300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>185200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>138000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>103100</v>
-      </c>
-      <c r="L43" s="3">
-        <v>80400</v>
       </c>
       <c r="M43" s="3">
         <v>80400</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
+      <c r="N43" s="3">
+        <v>80400</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
@@ -2123,9 +2215,12 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2150,8 +2245,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2168,44 +2263,47 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>4500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2400</v>
       </c>
       <c r="H45" s="3">
         <v>2400</v>
       </c>
       <c r="I45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J45" s="3">
         <v>11600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>24500</v>
       </c>
       <c r="M45" s="3">
         <v>24500</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="N45" s="3">
+        <v>24500</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
@@ -2213,44 +2311,47 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1489300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1567700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1631000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1319600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1162300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>943900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>984500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>418800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>314100</v>
-      </c>
-      <c r="L46" s="3">
-        <v>333300</v>
       </c>
       <c r="M46" s="3">
         <v>333300</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
+      <c r="N46" s="3">
+        <v>333300</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
@@ -2258,33 +2359,36 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>148800</v>
+      </c>
+      <c r="E47" s="3">
         <v>135200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>198500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>107300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>98700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>255200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>164200</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2300,47 +2404,50 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E48" s="3">
         <v>368400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>341400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>310700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>324400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>278100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>75800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>63000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>63700</v>
-      </c>
-      <c r="L48" s="3">
-        <v>36800</v>
       </c>
       <c r="M48" s="3">
         <v>36800</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3">
+        <v>36800</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
@@ -2348,44 +2455,47 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>530900</v>
+      </c>
+      <c r="E49" s="3">
         <v>404000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>423900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>453900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>472000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>251400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>269400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>51500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>58800</v>
-      </c>
-      <c r="L49" s="3">
-        <v>66900</v>
       </c>
       <c r="M49" s="3">
         <v>66900</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="N49" s="3">
+        <v>66900</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
@@ -2393,9 +2503,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,44 +2599,47 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>21600</v>
+        <v>43500</v>
       </c>
       <c r="E52" s="3">
+        <v>19600</v>
+      </c>
+      <c r="F52" s="3">
         <v>17500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>7500</v>
       </c>
       <c r="J52" s="3">
         <v>7500</v>
       </c>
       <c r="K52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="L52" s="3">
         <v>63100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>49400</v>
       </c>
       <c r="M52" s="3">
         <v>49400</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>49400</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2528,9 +2647,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,44 +2695,47 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4012700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2971300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3012700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2541300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2336500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1891100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1615400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>620000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>499600</v>
-      </c>
-      <c r="L54" s="3">
-        <v>486500</v>
       </c>
       <c r="M54" s="3">
         <v>486500</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
+      <c r="N54" s="3">
+        <v>486500</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
@@ -2618,9 +2743,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,43 +2786,44 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E57" s="3">
         <v>19000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>52800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>37400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>13400</v>
       </c>
       <c r="M57" s="3">
         <v>13400</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
+      <c r="N57" s="3">
+        <v>13400</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
@@ -2701,35 +2831,38 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E58" s="3">
         <v>22200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>746900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>37400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>53400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20700</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2737,8 +2870,8 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2746,44 +2879,47 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1455400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1320100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1172900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1029900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>779600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>507600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>397400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>283500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>250800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>187400</v>
       </c>
       <c r="M59" s="3">
         <v>187400</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
+      <c r="N59" s="3">
+        <v>187400</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
@@ -2791,44 +2927,47 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1831900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1660600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2208300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1371600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1093200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>694000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>516300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>373800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>269900</v>
-      </c>
-      <c r="L60" s="3">
-        <v>200900</v>
       </c>
       <c r="M60" s="3">
         <v>200900</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
+      <c r="N60" s="3">
+        <v>200900</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
@@ -2836,33 +2975,36 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>105400</v>
+      </c>
+      <c r="E61" s="3">
         <v>120800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>141300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>844800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>862300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>627800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>438900</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2881,44 +3023,47 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E62" s="3">
         <v>21300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>32300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>33900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>27100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>31100</v>
-      </c>
-      <c r="L62" s="3">
-        <v>17200</v>
       </c>
       <c r="M62" s="3">
         <v>17200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>17200</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -2926,9 +3071,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,44 +3215,47 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2010000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1841600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2395400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2265800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2010800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1344800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1001100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>411100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>301000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>218000</v>
       </c>
       <c r="M66" s="3">
         <v>218000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
+      <c r="N66" s="3">
+        <v>218000</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
@@ -3106,9 +3263,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3240,19 +3407,19 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>547500</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>546000</v>
-      </c>
-      <c r="L70" s="3">
-        <v>544600</v>
       </c>
       <c r="M70" s="3">
         <v>544600</v>
       </c>
       <c r="N70" s="3">
-        <v>0</v>
+        <v>544600</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,44 +3475,47 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1287300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1670200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1598700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1438200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1380500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1137200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-928800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-502300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-450000</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-334600</v>
       </c>
       <c r="M72" s="3">
         <v>-334600</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
+      <c r="N72" s="3">
+        <v>-334600</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
@@ -3350,9 +3523,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,44 +3667,47 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2002700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1129700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>617300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>275500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>325700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>546300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>614400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-338600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-347300</v>
-      </c>
-      <c r="L76" s="3">
-        <v>-276200</v>
       </c>
       <c r="M76" s="3">
         <v>-276200</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
+      <c r="N76" s="3">
+        <v>-276200</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
@@ -3530,9 +3715,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,47 +3763,50 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44957</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44592</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43861</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43496</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43131</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42766</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42400</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3625,42 +3816,45 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1067900</v>
+      </c>
+      <c r="E81" s="3">
         <v>74000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-97500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-70000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-243300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-208400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-426500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-52300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-116900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-124000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3670,9 +3864,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,38 +3887,39 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E83" s="3">
         <v>40600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>45800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>46800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>39300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>28400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>22100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>18100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>28500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3734,9 +3932,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,39 +4172,42 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1017300</v>
+      </c>
+      <c r="E89" s="3">
         <v>979500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>506800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>506500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>297000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>115700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>76100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>55000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,9 +4220,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,38 +4243,39 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-92400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-77700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-61400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-82400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-72000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-43300</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,9 +4288,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,39 +4384,42 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-312900</v>
+      </c>
+      <c r="E94" s="3">
         <v>44600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-191200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-162900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>81200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-321500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-664300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-40900</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4203,9 +4432,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4455,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4267,9 +4500,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,39 +4644,42 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-838800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-946000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-98300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-394600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-59000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-70500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>853100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>25700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4447,39 +4692,42 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4492,39 +4740,42 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-141900</v>
+      </c>
+      <c r="E102" s="3">
         <v>78300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>213500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-56700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>324900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-276700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>260700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>66200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-38000</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4537,7 +4788,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/DOCU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOCU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
   <si>
     <t>DOCU</t>
   </si>
@@ -656,65 +656,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44592</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44227</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43861</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43496</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43131</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42766</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42400</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -724,45 +724,48 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3219500</v>
+      </c>
+      <c r="E8" s="3">
         <v>2976700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2761900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2515900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2107200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1453000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>974000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>701000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>518500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>381500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>250500</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -772,45 +775,48 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>657600</v>
+      </c>
+      <c r="E9" s="3">
         <v>617800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>569600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>532800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>431600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>358200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>240700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>190400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>118300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>102500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>73900</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -820,45 +826,48 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2561900</v>
+      </c>
+      <c r="E10" s="3">
         <v>2359000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2192200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1983100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1675600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1094900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>733300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>510600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>400200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>279000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>176600</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -868,9 +877,12 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,44 +901,45 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>665000</v>
+      </c>
+      <c r="E12" s="3">
         <v>588500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>539500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>480600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>393400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>271500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>185600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>186000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>92400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>89700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>62300</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,36 +1000,39 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>34100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>31100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>33100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>33800</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,8 +1042,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1032,45 +1051,48 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E15" s="3">
         <v>52600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>60000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>66600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>71600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>64900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>46100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>28200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2000</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,9 +1102,12 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,44 +1123,45 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2920900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2742800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2699100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2574500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2164000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1626900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1167500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1127200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>570200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>497300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>369800</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1145,45 +1171,48 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>298600</v>
+      </c>
+      <c r="E18" s="3">
         <v>234000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>62700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-58600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-56800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-173900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-193500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-426200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-51700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-115800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-119300</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1193,9 +1222,12 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,8 +1246,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1228,30 +1261,30 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>3900</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-9000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3500</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,42 +1294,45 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>338200</v>
+      </c>
+      <c r="E21" s="3">
         <v>286600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>122700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-109000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-147400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-382000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-21500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-86000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1309,45 +1345,48 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="3">
         <v>1600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6800</v>
-      </c>
-      <c r="F22" s="3">
-        <v>6400</v>
       </c>
       <c r="G22" s="3">
         <v>6400</v>
       </c>
       <c r="H22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I22" s="3">
         <v>30800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>29300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10800</v>
-      </c>
-      <c r="K22" s="3">
-        <v>600</v>
       </c>
       <c r="L22" s="3">
         <v>600</v>
       </c>
       <c r="M22" s="3">
+        <v>600</v>
+      </c>
+      <c r="N22" s="3">
         <v>800</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1357,45 +1396,48 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>347300</v>
+      </c>
+      <c r="E23" s="3">
         <v>247900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>93700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-89900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-66900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-229500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-203600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-428200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-49100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-115100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-123600</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1405,45 +1447,48 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-819900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1000</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1453,9 +1498,12 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,45 +1549,48 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>309100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1067900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>74000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-97500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-70000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-243300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-208400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-426500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-52300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-115400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-122600</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1549,45 +1600,48 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>309100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1067900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>74000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-97500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-70000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-243300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-208400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-426800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-53700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-116900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-124000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1597,9 +1651,12 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1693,9 +1753,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,9 +1855,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1804,30 +1873,30 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>-3900</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>9000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3500</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1837,45 +1906,48 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>309100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1067900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>74000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-97500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-70000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-243300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-208400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-426500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-52300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-116900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-124000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1885,9 +1957,12 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,45 +2008,48 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>309100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1067900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>74000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-97500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-70000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-243300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-208400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-426500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-52300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-116900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-124000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1981,50 +2059,53 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44592</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44227</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43861</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43496</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43131</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42766</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42400</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2034,9 +2115,12 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,46 +2160,47 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>602400</v>
+      </c>
+      <c r="E41" s="3">
         <v>648600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>797100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>721900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>509100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>566100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>241200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>517800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>256900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>190600</v>
-      </c>
-      <c r="M41" s="3">
-        <v>228500</v>
       </c>
       <c r="N41" s="3">
         <v>228500</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
+      <c r="O41" s="3">
+        <v>228500</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
@@ -2122,38 +2208,41 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>264100</v>
+      </c>
+      <c r="E42" s="3">
         <v>314900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>248400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>309800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>293800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>207500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>414900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>251200</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -2167,50 +2256,53 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>527200</v>
+      </c>
+      <c r="E43" s="3">
         <v>443300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>455200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>529400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>453500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>340500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>250300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>185200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>138000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>103100</v>
-      </c>
-      <c r="M43" s="3">
-        <v>80400</v>
       </c>
       <c r="N43" s="3">
         <v>80400</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
+      <c r="O43" s="3">
+        <v>80400</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
@@ -2218,9 +2310,12 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2248,8 +2343,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2266,47 +2361,50 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>4500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2400</v>
       </c>
       <c r="I45" s="3">
         <v>2400</v>
       </c>
       <c r="J45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K45" s="3">
         <v>11600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>20500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>24500</v>
       </c>
       <c r="N45" s="3">
         <v>24500</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>24500</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
@@ -2314,47 +2412,50 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1490800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1489300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1567700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1631000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1319600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1162300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>943900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>984500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>418800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>314100</v>
-      </c>
-      <c r="M46" s="3">
-        <v>333300</v>
       </c>
       <c r="N46" s="3">
         <v>333300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
+      <c r="O46" s="3">
+        <v>333300</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
@@ -2362,36 +2463,39 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>223500</v>
+      </c>
+      <c r="E47" s="3">
         <v>148800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>135200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>198500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>107300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>98700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>255200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>164200</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2407,50 +2511,53 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>527400</v>
+      </c>
+      <c r="E48" s="3">
         <v>409000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>368400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>341400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>310700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>324400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>278100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>75800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>63000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>63700</v>
-      </c>
-      <c r="M48" s="3">
-        <v>36800</v>
       </c>
       <c r="N48" s="3">
         <v>36800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>36800</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
@@ -2458,47 +2565,50 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>519800</v>
+      </c>
+      <c r="E49" s="3">
         <v>530900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>404000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>423900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>453900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>472000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>251400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>269400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>51500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>58800</v>
-      </c>
-      <c r="M49" s="3">
-        <v>66900</v>
       </c>
       <c r="N49" s="3">
         <v>66900</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>66900</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
@@ -2506,9 +2616,12 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,47 +2718,50 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E52" s="3">
         <v>43500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>7500</v>
       </c>
       <c r="K52" s="3">
         <v>7500</v>
       </c>
       <c r="L52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="M52" s="3">
         <v>63100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>49400</v>
       </c>
       <c r="N52" s="3">
         <v>49400</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>49400</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -2650,9 +2769,12 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,47 +2820,50 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4229600</v>
+      </c>
+      <c r="E54" s="3">
         <v>4012700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2971300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3012700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2541300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2336500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1891100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1615400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>620000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>499600</v>
-      </c>
-      <c r="M54" s="3">
-        <v>486500</v>
       </c>
       <c r="N54" s="3">
         <v>486500</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
+      <c r="O54" s="3">
+        <v>486500</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
@@ -2746,9 +2871,12 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,46 +2916,47 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E57" s="3">
         <v>30700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>52800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>37400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>13400</v>
       </c>
       <c r="N57" s="3">
         <v>13400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="O57" s="3">
+        <v>13400</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
@@ -2834,38 +2964,41 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E58" s="3">
         <v>19100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>22200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>746900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>37400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>53400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20700</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2873,8 +3006,8 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2882,47 +3015,50 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1631200</v>
+      </c>
+      <c r="E59" s="3">
         <v>1455400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1320100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1172900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1029900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>779600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>507600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>397400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>283500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>250800</v>
-      </c>
-      <c r="M59" s="3">
-        <v>187400</v>
       </c>
       <c r="N59" s="3">
         <v>187400</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3">
+        <v>187400</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
@@ -2930,47 +3066,50 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2039400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1831900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1660600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2208300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1371600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1093200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>694000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>516300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>373800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>269900</v>
-      </c>
-      <c r="M60" s="3">
-        <v>200900</v>
       </c>
       <c r="N60" s="3">
         <v>200900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
+      <c r="O60" s="3">
+        <v>200900</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
@@ -2978,36 +3117,39 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>168500</v>
+      </c>
+      <c r="E61" s="3">
         <v>105400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>120800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>141300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>844800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>862300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>627800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>438900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3026,47 +3168,50 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E62" s="3">
         <v>30600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>32300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>33900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>27100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>31100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>17200</v>
       </c>
       <c r="N62" s="3">
         <v>17200</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
+      <c r="O62" s="3">
+        <v>17200</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
@@ -3074,9 +3219,12 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,47 +3372,50 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2311700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2010000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1841600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2395400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2265800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2010800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1344800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1001100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>411100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>301000</v>
-      </c>
-      <c r="M66" s="3">
-        <v>218000</v>
       </c>
       <c r="N66" s="3">
         <v>218000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
+      <c r="O66" s="3">
+        <v>218000</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
@@ -3266,9 +3423,12 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3410,19 +3577,19 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>547500</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>546000</v>
-      </c>
-      <c r="M70" s="3">
-        <v>544600</v>
       </c>
       <c r="N70" s="3">
         <v>544600</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
+        <v>544600</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,47 +3648,50 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1856500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1287300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1670200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1598700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1438200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1380500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1137200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-928800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-502300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-450000</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-334600</v>
       </c>
       <c r="N72" s="3">
         <v>-334600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
+      <c r="O72" s="3">
+        <v>-334600</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
@@ -3526,9 +3699,12 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,47 +3852,50 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1917800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2002700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1129700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>617300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>275500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>325700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>546300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>614400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-338600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-347300</v>
-      </c>
-      <c r="M76" s="3">
-        <v>-276200</v>
       </c>
       <c r="N76" s="3">
         <v>-276200</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
+      <c r="O76" s="3">
+        <v>-276200</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
@@ -3718,9 +3903,12 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,50 +3954,53 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44592</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44227</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43861</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43496</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43131</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42766</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42400</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3819,45 +4010,48 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>309100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1067900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>74000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-97500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-70000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-243300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-208400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-426500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-52300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-116900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-124000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,9 +4061,12 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,41 +4085,42 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E83" s="3">
         <v>27900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>40600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>46800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>39300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>28400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>22100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>18100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>28500</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3935,9 +4133,12 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,42 +4388,45 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1165000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1017300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>979500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>506800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>506500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>297000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>115700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>76100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>55000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4800</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,9 +4439,12 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,41 +4463,42 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-106400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-97000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-92400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-77700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-61400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-82400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-72000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-30400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-18900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-43300</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4291,9 +4511,12 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,42 +4613,45 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-126800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-312900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>44600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-191200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-162900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>81200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-321500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-664300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-18800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-40900</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4435,9 +4664,12 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,8 +4688,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4503,9 +4736,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,42 +4889,45 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1099900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-838800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-946000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-98300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-394600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-59000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-70500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>853100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>25700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4695,42 +4940,45 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4743,42 +4991,45 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-141900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>78300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>213500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-56700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>324900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-276700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>260700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>66200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-38000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,7 +5042,10 @@
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
